--- a/assets/constructions/examples/ctd_rm_head.xlsx
+++ b/assets/constructions/examples/ctd_rm_head.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:BC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,11 +679,36 @@
           <t>brazed</t>
         </is>
       </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PMX5-12H7-EB45 RX2000</t>
+          <t>PMX6-21H7-EB45 RX2000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -698,7 +723,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SECO_RMX06</t>
+          <t>SECO_RMX08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -713,7 +738,7 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -730,16 +755,16 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>SECO_RMX06</t>
+          <t>SECO_RMX08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -782,11 +807,11 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr"/>
@@ -799,16 +824,581 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2018/Обработка отверстий.pdf</t>
+          <t>2020 / Обработка отверстий</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>THROUGH</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PMX6-27H7-EB45 RX2000</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SECO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Precimaster Plus</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SECO_RMX12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SECO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>27</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>8</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>12</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>SECO_RMX12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>RX2000</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2020 / Обработка отверстий</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>THROUGH</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PMX6-10H7-EB45 RX2000</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SECO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Precimaster Plus</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SECO_RMX06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SECO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>7</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>SECO_RMX06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>RX2000</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2020 / Обработка отверстий</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>THROUGH</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PMX6-26H7-EB45 RX2000</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SECO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Precimaster Plus</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SECO_RMX12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SECO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>12</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>SECO_RMX12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>RX2000</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2020 / Обработка отверстий</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>THROUGH</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PMX6-23H7-EB45 RX2000</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SECO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Precimaster Plus</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SECO_RMX12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SECO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>23</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>8</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>12</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>12</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>SECO_RMX12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>RX2000</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2020 / Обработка отверстий</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>THROUGH</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
